--- a/data/base/Backlog_2.xlsx
+++ b/data/base/Backlog_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duasrodas-my.sharepoint.com/personal/francisco_pereira_duasrodas_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B9258B19-43B2-497D-B236-7970109310D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB692528-488D-4E87-8981-87F6ED10AB08}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92661375-B2C2-483D-99F9-F151987A5D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F6B3BDBE-1840-498F-8889-731B830C699A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F6B3BDBE-1840-498F-8889-731B830C699A}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
   <si>
     <t>Setor</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Mateus Neckel</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -207,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -226,6 +229,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,19 +570,21 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="8"/>
+    <col min="11" max="11" width="17" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -632,7 +641,7 @@
       <c r="G2" s="7">
         <v>8282</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="9">
         <v>46023</v>
       </c>
       <c r="I2" s="3">
@@ -645,7 +654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -667,20 +676,20 @@
       <c r="G3" s="7">
         <v>8337</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="9">
         <v>46023</v>
       </c>
       <c r="I3" s="3">
         <v>46041</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +711,7 @@
       <c r="G4" s="7">
         <v>8372</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="9">
         <v>46023</v>
       </c>
       <c r="I4" s="3">
@@ -715,7 +724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -737,20 +746,20 @@
       <c r="G5" s="7">
         <v>8518</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="9">
         <v>46023</v>
       </c>
       <c r="I5" s="3">
         <v>46041</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -772,20 +781,20 @@
       <c r="G6" s="7">
         <v>8541</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="9">
         <v>46023</v>
       </c>
       <c r="I6" s="3">
         <v>46041</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -807,20 +816,20 @@
       <c r="G7" s="7">
         <v>8555</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="9">
         <v>46023</v>
       </c>
       <c r="I7" s="3">
         <v>46041</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -842,7 +851,7 @@
       <c r="G8" s="7">
         <v>8571</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="9">
         <v>46023</v>
       </c>
       <c r="I8" s="3">
@@ -855,7 +864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -877,20 +886,20 @@
       <c r="G9" s="7">
         <v>8647</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="9">
         <v>46023</v>
       </c>
       <c r="I9" s="3">
         <v>46041</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -912,20 +921,20 @@
       <c r="G10" s="7">
         <v>8699</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="9">
         <v>46023</v>
       </c>
       <c r="I10" s="3">
         <v>46041</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -947,20 +956,20 @@
       <c r="G11" s="7">
         <v>8715</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="9">
         <v>46023</v>
       </c>
       <c r="I11" s="3">
         <v>46041</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
@@ -982,20 +991,20 @@
       <c r="G12" s="7">
         <v>8723</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="9">
         <v>46023</v>
       </c>
       <c r="I12" s="3">
         <v>46041</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -1017,20 +1026,20 @@
       <c r="G13" s="7">
         <v>8757</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="9">
         <v>46023</v>
       </c>
       <c r="I13" s="3">
         <v>46041</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -1052,14 +1061,14 @@
       <c r="G14" s="7">
         <v>8860</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="9">
         <v>46023</v>
       </c>
       <c r="I14" s="3">
         <v>46041</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>18</v>
@@ -1074,6 +1083,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7E7759-DDF2-4F46-A0B0-3738C6A46F81}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1139,7 +1160,7 @@
         <v>46041</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>14</v>
@@ -1174,7 +1195,7 @@
         <v>46041</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>14</v>
@@ -1209,7 +1230,7 @@
         <v>46041</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>14</v>
